--- a/data/output/2025/evaluasi_61.xlsx
+++ b/data/output/2025/evaluasi_61.xlsx
@@ -2249,7 +2249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2337,6 +2337,258 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.448516776523913</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>39.57998277195529</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.88476521309426</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.620814066845447</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.251218333713886</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.9963468036740964</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.6680319642230487</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7619168283706388</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.389380908426092</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2495,6 +2747,230 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.251191394709909</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>46.01349114863319</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.44516449094481</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1409263238192519</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.577458491069146</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.6338590526978413</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9261517042666515</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.575176623292877</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2709,6 +3185,258 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.33609116633226</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>38.53631112109272</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.10344437216548</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8957748992514811</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4813940563777044</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3949546150423345</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.0200581100887116</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.15277132362982</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.453073184930564</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2723,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2923,6 +3651,286 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.851691174924539</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>31.65782489450337</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.838109699914305</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.365250012987972</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.798601814204002</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.32141358359428</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.006448520187411737</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2555024022984598</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6933684849324381</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.526327255638382</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2937,7 +3945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3109,6 +4117,314 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.31301855356365</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.841292296740292</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>44.02297944737234</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>79.06993669343483</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.57031795736678</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.666931048697057</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>69.37168515389345</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.017857956390269</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>19.23727016659818</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1238332210692587</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2263813011794004</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3123,7 +4439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,6 +4555,286 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.81114616622436</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>43.10302679371307</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.36549561617488</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.221788326005925</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6641968169251571</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.87688036650929</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.429007915885605</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.03118611186395</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6210330416271405</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.186356997615468</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3253,7 +4849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3509,6 +5105,258 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.339999999999999</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>36.41000000000002</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.06526131090912</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.54426078869252</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.725623700778595</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4342195607694326</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3505378539136129</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6173686314791645</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.267569838546379</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3523,7 +5371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3779,6 +5627,286 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.224623406077155</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>38.62245642944174</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>17.04420501199079</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.834767798188562</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.76522335850212</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.4160221775359668</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.579817140476771</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.159175507379523</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.667964410655292</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-3.1462942861021</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3793,7 +5921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4021,6 +6149,286 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.436115434631387</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>39.43088236602271</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.27278650017547</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.17287422985723</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.208843328039123</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.198039550105378</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5729296762706285</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.145824498843892</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5962853657665914</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.304646352304723</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4035,7 +6443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4235,6 +6643,286 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.067055014859004</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>34.06649492423246</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.03293424272121</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.996626757426556</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.444404509352941</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.01831992678707</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.10378877013842</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.237452791175477</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2426151038268548</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.422729555255634</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4249,7 +6937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4421,6 +7109,286 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.606330533816704</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>47.79773679167742</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.92030307718388</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.563882082136426</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.860537943736352</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.008305359811164</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.930527791605266</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3448970141813632</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7918027495113538</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5063840642688875</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4435,7 +7403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4607,6 +7575,286 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.32382963180158</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>38.06741806638362</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.78872127839336</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.663306351136649</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.479723941348302</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.045788506844117</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7714675612530713</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3218077172941823</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.07693865180432</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4529363561075453</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4621,7 +7869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4821,6 +8069,258 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.51429079799107</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40.37890256639668</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.67988061104187</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.329359361613552</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.013102319363034</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9837656614408193</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.368347503996039</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.029553932292057</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.310915181603459</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4835,7 +8335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4898,6 +8398,230 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.172830255041537</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>35.83523654358512</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.80406228714656</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.754951682916463</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2205431219279682</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1160140791498227</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.00272106825752544</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6709280785397758</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
